--- a/Temp/20260622_134619/SSCUI_102665_OPN.xlsx
+++ b/Temp/20260622_134619/SSCUI_102665_OPN.xlsx
@@ -1,32 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_D536C3608C1C35E513B396C45ECD8ECF6A9F5E36" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C919BC36-A0C9-4A27-9AD3-081817288943}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="SSCUI Mapping" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -615,7 +598,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -692,21 +675,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -744,7 +719,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -778,7 +753,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -813,10 +787,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -989,13 +962,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E411"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="53.140625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -7407,423 +7376,417 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B5" r:id="rId4" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B6" r:id="rId5" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B7" r:id="rId6" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B8" r:id="rId7" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="B9" r:id="rId8" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B10" r:id="rId9" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B11" r:id="rId10" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B12" r:id="rId11" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B13" r:id="rId12" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B14" r:id="rId13" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="B15" r:id="rId14" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B16" r:id="rId15" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B17" r:id="rId16" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B18" r:id="rId17" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B19" r:id="rId18" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="B20" r:id="rId19" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B21" r:id="rId20" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="B22" r:id="rId21" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B23" r:id="rId22" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B24" r:id="rId23" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B25" r:id="rId24" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B26" r:id="rId25" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B27" r:id="rId26" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B28" r:id="rId27" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="B29" r:id="rId28" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B30" r:id="rId29" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B31" r:id="rId30" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="B32" r:id="rId31" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B33" r:id="rId32" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B34" r:id="rId33" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B35" r:id="rId34" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B36" r:id="rId35" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="B37" r:id="rId36" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B38" r:id="rId37" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B39" r:id="rId38" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B40" r:id="rId39" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B41" r:id="rId40" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B42" r:id="rId41" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B43" r:id="rId42" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B44" r:id="rId43" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B45" r:id="rId44" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B46" r:id="rId45" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B47" r:id="rId46" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="B48" r:id="rId47" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B49" r:id="rId48" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B50" r:id="rId49" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B51" r:id="rId50" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="B52" r:id="rId51" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="B53" r:id="rId52" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B54" r:id="rId53" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B55" r:id="rId54" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="B56" r:id="rId55" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="B57" r:id="rId56" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="B58" r:id="rId57" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="B59" r:id="rId58" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="B60" r:id="rId59" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="B61" r:id="rId60" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="B62" r:id="rId61" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="B63" r:id="rId62" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="B64" r:id="rId63" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="B65" r:id="rId64" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="B66" r:id="rId65" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="B67" r:id="rId66" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="B68" r:id="rId67" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="B69" r:id="rId68" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="B70" r:id="rId69" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="B71" r:id="rId70" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="B72" r:id="rId71" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="B73" r:id="rId72" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="B74" r:id="rId73" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="B75" r:id="rId74" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="B76" r:id="rId75" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="B77" r:id="rId76" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="B78" r:id="rId77" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="B79" r:id="rId78" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="B80" r:id="rId79" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="B81" r:id="rId80" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="B82" r:id="rId81" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="B83" r:id="rId82" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="B84" r:id="rId83" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="B85" r:id="rId84" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="B86" r:id="rId85" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="B87" r:id="rId86" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="B88" r:id="rId87" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="B89" r:id="rId88" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="B90" r:id="rId89" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="B91" r:id="rId90" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="B92" r:id="rId91" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="B93" r:id="rId92" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="B94" r:id="rId93" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="B95" r:id="rId94" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="B96" r:id="rId95" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="B97" r:id="rId96" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="B98" r:id="rId97" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="B99" r:id="rId98" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="B100" r:id="rId99" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="B101" r:id="rId100" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="B102" r:id="rId101" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="B103" r:id="rId102" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="B104" r:id="rId103" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="B105" r:id="rId104" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="B106" r:id="rId105" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="B107" r:id="rId106" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="B108" r:id="rId107" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="B109" r:id="rId108" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="B110" r:id="rId109" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="B111" r:id="rId110" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="B112" r:id="rId111" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="B113" r:id="rId112" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="B114" r:id="rId113" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="B115" r:id="rId114" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="B116" r:id="rId115" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="B117" r:id="rId116" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="B118" r:id="rId117" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="B119" r:id="rId118" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="B120" r:id="rId119" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="B121" r:id="rId120" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="B122" r:id="rId121" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="B123" r:id="rId122" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="B124" r:id="rId123" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="B125" r:id="rId124" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="B126" r:id="rId125" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="B127" r:id="rId126" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="B128" r:id="rId127" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="B129" r:id="rId128" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="B130" r:id="rId129" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="B131" r:id="rId130" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="B132" r:id="rId131" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="B133" r:id="rId132" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="B134" r:id="rId133" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="B135" r:id="rId134" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="B136" r:id="rId135" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="B137" r:id="rId136" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="B138" r:id="rId137" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="B139" r:id="rId138" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="B140" r:id="rId139" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="B141" r:id="rId140" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="B142" r:id="rId141" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="B143" r:id="rId142" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="B144" r:id="rId143" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="B145" r:id="rId144" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="B146" r:id="rId145" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="B147" r:id="rId146" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="B148" r:id="rId147" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="B149" r:id="rId148" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="B150" r:id="rId149" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="B151" r:id="rId150" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="B152" r:id="rId151" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="B153" r:id="rId152" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="B154" r:id="rId153" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="B155" r:id="rId154" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="B156" r:id="rId155" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="B157" r:id="rId156" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="B158" r:id="rId157" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="B159" r:id="rId158" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="B160" r:id="rId159" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="B161" r:id="rId160" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="B162" r:id="rId161" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="B163" r:id="rId162" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="B164" r:id="rId163" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="B165" r:id="rId164" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="B166" r:id="rId165" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="B167" r:id="rId166" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="B168" r:id="rId167" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="B169" r:id="rId168" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="B170" r:id="rId169" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="B171" r:id="rId170" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="B172" r:id="rId171" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="B173" r:id="rId172" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="B174" r:id="rId173" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="B175" r:id="rId174" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="B176" r:id="rId175" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="B177" r:id="rId176" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="B178" r:id="rId177" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="B179" r:id="rId178" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="B180" r:id="rId179" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="B181" r:id="rId180" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="B182" r:id="rId181" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="B183" r:id="rId182" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="B184" r:id="rId183" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="B185" r:id="rId184" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="B186" r:id="rId185" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="B187" r:id="rId186" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="B188" r:id="rId187" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="B189" r:id="rId188" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="B190" r:id="rId189" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="B191" r:id="rId190" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="B192" r:id="rId191" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="B193" r:id="rId192" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="B194" r:id="rId193" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="B195" r:id="rId194" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="B196" r:id="rId195" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="B197" r:id="rId196" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="B198" r:id="rId197" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="B199" r:id="rId198" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="B200" r:id="rId199" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="B201" r:id="rId200" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="B202" r:id="rId201" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="B203" r:id="rId202" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="B204" r:id="rId203" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="B205" r:id="rId204" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="B206" r:id="rId205" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="B207" r:id="rId206" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="B208" r:id="rId207" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="B209" r:id="rId208" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="B210" r:id="rId209" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="B211" r:id="rId210" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="B212" r:id="rId211" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="B213" r:id="rId212" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="B214" r:id="rId213" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="B215" r:id="rId214" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="B216" r:id="rId215" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="B217" r:id="rId216" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="B218" r:id="rId217" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="B219" r:id="rId218" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="B220" r:id="rId219" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="B221" r:id="rId220" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="B222" r:id="rId221" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="B223" r:id="rId222" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="B224" r:id="rId223" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="B225" r:id="rId224" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="B226" r:id="rId225" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="B227" r:id="rId226" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="B228" r:id="rId227" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="B229" r:id="rId228" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="B230" r:id="rId229" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="B231" r:id="rId230" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="B232" r:id="rId231" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="B233" r:id="rId232" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="B234" r:id="rId233" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="B235" r:id="rId234" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="B236" r:id="rId235" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="B237" r:id="rId236" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="B238" r:id="rId237" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="B239" r:id="rId238" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="B240" r:id="rId239" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="B241" r:id="rId240" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="B242" r:id="rId241" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="B243" r:id="rId242" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="B244" r:id="rId243" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="B245" r:id="rId244" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="B246" r:id="rId245" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="B247" r:id="rId246" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="B248" r:id="rId247" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="B249" r:id="rId248" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="B250" r:id="rId249" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="B251" r:id="rId250" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="B252" r:id="rId251" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="B253" r:id="rId252" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="B254" r:id="rId253" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="B255" r:id="rId254" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="B256" r:id="rId255" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="B257" r:id="rId256" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="B258" r:id="rId257" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="B259" r:id="rId258" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="B260" r:id="rId259" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="B261" r:id="rId260" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="B262" r:id="rId261" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="B263" r:id="rId262" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="B264" r:id="rId263" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="B265" r:id="rId264" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="B266" r:id="rId265" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="B267" r:id="rId266" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="B268" r:id="rId267" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="B269" r:id="rId268" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="B270" r:id="rId269" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="B271" r:id="rId270" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="B272" r:id="rId271" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="B273" r:id="rId272" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="B274" r:id="rId273" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="B275" r:id="rId274" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="B276" r:id="rId275" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="B277" r:id="rId276" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="B278" r:id="rId277" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="B279" r:id="rId278" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="B280" r:id="rId279" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="B281" r:id="rId280" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="B282" r:id="rId281" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="B283" r:id="rId282" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="B284" r:id="rId283" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="B285" r:id="rId284" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="B286" r:id="rId285" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="B287" r:id="rId286" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="B288" r:id="rId287" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="B289" r:id="rId288" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="B290" r:id="rId289" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="B291" r:id="rId290" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="B292" r:id="rId291" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="B293" r:id="rId292" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="B294" r:id="rId293" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="B295" r:id="rId294" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="B296" r:id="rId295" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="B297" r:id="rId296" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="B298" r:id="rId297" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="B299" r:id="rId298" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="B300" r:id="rId299" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="B301" r:id="rId300" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="B302" r:id="rId301" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="B303" r:id="rId302" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="B304" r:id="rId303" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="B305" r:id="rId304" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="B306" r:id="rId305" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="B307" r:id="rId306" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="B308" r:id="rId307" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="B309" r:id="rId308" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="B310" r:id="rId309" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="B311" r:id="rId310" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="B312" r:id="rId311" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="B313" r:id="rId312" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="B314" r:id="rId313" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="B315" r:id="rId314" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="B316" r:id="rId315" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="B317" r:id="rId316" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="B318" r:id="rId317" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="B319" r:id="rId318" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="B320" r:id="rId319" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="B321" r:id="rId320" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="B322" r:id="rId321" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="B323" r:id="rId322" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="B324" r:id="rId323" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="B325" r:id="rId324" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="B326" r:id="rId325" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="B327" r:id="rId326" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="B328" r:id="rId327" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="B329" r:id="rId328" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="B330" r:id="rId329" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="B331" r:id="rId330" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="B332" r:id="rId331" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="B333" r:id="rId332" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="B334" r:id="rId333" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="B335" r:id="rId334" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="B336" r:id="rId335" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="B337" r:id="rId336" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="B338" r:id="rId337" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="B339" r:id="rId338" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="B340" r:id="rId339" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="B341" r:id="rId340" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="B342" r:id="rId341" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="B343" r:id="rId342" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="B344" r:id="rId343" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="B345" r:id="rId344" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="B346" r:id="rId345" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="B347" r:id="rId346" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="B348" r:id="rId347" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="B349" r:id="rId348" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="B350" r:id="rId349" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="B351" r:id="rId350" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="B352" r:id="rId351" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="B353" r:id="rId352" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="B354" r:id="rId353" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="B355" r:id="rId354" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="B356" r:id="rId355" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="B357" r:id="rId356" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="B358" r:id="rId357" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="B359" r:id="rId358" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="B360" r:id="rId359" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="B361" r:id="rId360" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="B362" r:id="rId361" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="B363" r:id="rId362" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="B364" r:id="rId363" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="B365" r:id="rId364" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="B366" r:id="rId365" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="B367" r:id="rId366" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="B368" r:id="rId367" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="B369" r:id="rId368" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="B370" r:id="rId369" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="B371" r:id="rId370" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="B372" r:id="rId371" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="B373" r:id="rId372" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="B374" r:id="rId373" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="B375" r:id="rId374" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="B376" r:id="rId375" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="B377" r:id="rId376" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="B378" r:id="rId377" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="B379" r:id="rId378" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="B380" r:id="rId379" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="B381" r:id="rId380" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="B382" r:id="rId381" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="B383" r:id="rId382" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="B384" r:id="rId383" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="B385" r:id="rId384" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="B386" r:id="rId385" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="B387" r:id="rId386" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="B388" r:id="rId387" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="B389" r:id="rId388" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="B390" r:id="rId389" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="B391" r:id="rId390" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="B392" r:id="rId391" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="B393" r:id="rId392" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="B394" r:id="rId393" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="B395" r:id="rId394" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="B396" r:id="rId395" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="B397" r:id="rId396" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="B398" r:id="rId397" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="B399" r:id="rId398" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="B400" r:id="rId399" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="B401" r:id="rId400" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="B402" r:id="rId401" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="B403" r:id="rId402" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="B404" r:id="rId403" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="B405" r:id="rId404" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="B406" r:id="rId405" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="B407" r:id="rId406" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="B408" r:id="rId407" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="B409" r:id="rId408" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="B410" r:id="rId409" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="B411" r:id="rId410" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="B2" r:id="rId1" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B3" r:id="rId2" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B4" r:id="rId3" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B5" r:id="rId4" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B6" r:id="rId5" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B7" r:id="rId6" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B8" r:id="rId7" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B9" r:id="rId8" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B10" r:id="rId9" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B11" r:id="rId10" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B12" r:id="rId11" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B13" r:id="rId12" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B14" r:id="rId13" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B15" r:id="rId14" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B16" r:id="rId15" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B17" r:id="rId16" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B18" r:id="rId17" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B19" r:id="rId18" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B20" r:id="rId19" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B21" r:id="rId20" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B22" r:id="rId21" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B23" r:id="rId22" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B24" r:id="rId23" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B25" r:id="rId24" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B26" r:id="rId25" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B27" r:id="rId26" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B28" r:id="rId27" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B29" r:id="rId28" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B30" r:id="rId29" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B31" r:id="rId30" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B32" r:id="rId31" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B33" r:id="rId32" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B34" r:id="rId33" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B35" r:id="rId34" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B36" r:id="rId35" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B37" r:id="rId36" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B38" r:id="rId37" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B39" r:id="rId38" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B40" r:id="rId39" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B41" r:id="rId40" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B42" r:id="rId41" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B43" r:id="rId42" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B44" r:id="rId43" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B45" r:id="rId44" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B46" r:id="rId45" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B47" r:id="rId46" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B48" r:id="rId47" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B49" r:id="rId48" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B50" r:id="rId49" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B51" r:id="rId50" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B52" r:id="rId51" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B53" r:id="rId52" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B54" r:id="rId53" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B55" r:id="rId54" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B56" r:id="rId55" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B57" r:id="rId56" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B58" r:id="rId57" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B59" r:id="rId58" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B60" r:id="rId59" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B61" r:id="rId60" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B62" r:id="rId61" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B63" r:id="rId62" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B64" r:id="rId63" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B65" r:id="rId64" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B66" r:id="rId65" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B67" r:id="rId66" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B68" r:id="rId67" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B69" r:id="rId68" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B70" r:id="rId69" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B71" r:id="rId70" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B72" r:id="rId71" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B73" r:id="rId72" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B74" r:id="rId73" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B75" r:id="rId74" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B76" r:id="rId75" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B77" r:id="rId76" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B78" r:id="rId77" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B79" r:id="rId78" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B80" r:id="rId79" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B81" r:id="rId80" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B82" r:id="rId81" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B83" r:id="rId82" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B84" r:id="rId83" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B85" r:id="rId84" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B86" r:id="rId85" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B87" r:id="rId86" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B88" r:id="rId87" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B89" r:id="rId88" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B90" r:id="rId89" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B91" r:id="rId90" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B92" r:id="rId91" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B93" r:id="rId92" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B94" r:id="rId93" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B95" r:id="rId94" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B96" r:id="rId95" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B97" r:id="rId96" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B98" r:id="rId97" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B99" r:id="rId98" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B100" r:id="rId99" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B101" r:id="rId100" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B102" r:id="rId101" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B103" r:id="rId102" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B104" r:id="rId103" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B105" r:id="rId104" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B106" r:id="rId105" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B107" r:id="rId106" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B108" r:id="rId107" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B109" r:id="rId108" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B110" r:id="rId109" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B111" r:id="rId110" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B112" r:id="rId111" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B113" r:id="rId112" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B114" r:id="rId113" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B115" r:id="rId114" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B116" r:id="rId115" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B117" r:id="rId116" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B118" r:id="rId117" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B119" r:id="rId118" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B120" r:id="rId119" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B121" r:id="rId120" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B122" r:id="rId121" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B123" r:id="rId122" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B124" r:id="rId123" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B125" r:id="rId124" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B126" r:id="rId125" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B127" r:id="rId126" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B128" r:id="rId127" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B129" r:id="rId128" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B130" r:id="rId129" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B131" r:id="rId130" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B132" r:id="rId131" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B133" r:id="rId132" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B134" r:id="rId133" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B135" r:id="rId134" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B136" r:id="rId135" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B137" r:id="rId136" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B138" r:id="rId137" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B139" r:id="rId138" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B140" r:id="rId139" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B141" r:id="rId140" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B142" r:id="rId141" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B143" r:id="rId142" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B144" r:id="rId143" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B145" r:id="rId144" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B146" r:id="rId145" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B147" r:id="rId146" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B148" r:id="rId147" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B149" r:id="rId148" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B150" r:id="rId149" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B151" r:id="rId150" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B152" r:id="rId151" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B153" r:id="rId152" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B154" r:id="rId153" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B155" r:id="rId154" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B156" r:id="rId155" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B157" r:id="rId156" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B158" r:id="rId157" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B159" r:id="rId158" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B160" r:id="rId159" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B161" r:id="rId160" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B162" r:id="rId161" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B163" r:id="rId162" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B164" r:id="rId163" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B165" r:id="rId164" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B166" r:id="rId165" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B167" r:id="rId166" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B168" r:id="rId167" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B169" r:id="rId168" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B170" r:id="rId169" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B171" r:id="rId170" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B172" r:id="rId171" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B173" r:id="rId172" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B174" r:id="rId173" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B175" r:id="rId174" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B176" r:id="rId175" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B177" r:id="rId176" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B178" r:id="rId177" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B179" r:id="rId178" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B180" r:id="rId179" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B181" r:id="rId180" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B182" r:id="rId181" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B183" r:id="rId182" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B184" r:id="rId183" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B185" r:id="rId184" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B186" r:id="rId185" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B187" r:id="rId186" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B188" r:id="rId187" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B189" r:id="rId188" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B190" r:id="rId189" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B191" r:id="rId190" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B192" r:id="rId191" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B193" r:id="rId192" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B194" r:id="rId193" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B195" r:id="rId194" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B196" r:id="rId195" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B197" r:id="rId196" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B198" r:id="rId197" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B199" r:id="rId198" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B200" r:id="rId199" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B201" r:id="rId200" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B202" r:id="rId201" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B203" r:id="rId202" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B204" r:id="rId203" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B205" r:id="rId204" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B206" r:id="rId205" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B207" r:id="rId206" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B208" r:id="rId207" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B209" r:id="rId208" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B210" r:id="rId209" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B211" r:id="rId210" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B212" r:id="rId211" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B213" r:id="rId212" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B214" r:id="rId213" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B215" r:id="rId214" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B216" r:id="rId215" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B217" r:id="rId216" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B218" r:id="rId217" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B219" r:id="rId218" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B220" r:id="rId219" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B221" r:id="rId220" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B222" r:id="rId221" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B223" r:id="rId222" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B224" r:id="rId223" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B225" r:id="rId224" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B226" r:id="rId225" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B227" r:id="rId226" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B228" r:id="rId227" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B229" r:id="rId228" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B230" r:id="rId229" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B231" r:id="rId230" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B232" r:id="rId231" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B233" r:id="rId232" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B234" r:id="rId233" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B235" r:id="rId234" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B236" r:id="rId235" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B237" r:id="rId236" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B238" r:id="rId237" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B239" r:id="rId238" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B240" r:id="rId239" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B241" r:id="rId240" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B242" r:id="rId241" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B243" r:id="rId242" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B244" r:id="rId243" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B245" r:id="rId244" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B246" r:id="rId245" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B247" r:id="rId246" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B248" r:id="rId247" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B249" r:id="rId248" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B250" r:id="rId249" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B251" r:id="rId250" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B252" r:id="rId251" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B253" r:id="rId252" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B254" r:id="rId253" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B255" r:id="rId254" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B256" r:id="rId255" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B257" r:id="rId256" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B258" r:id="rId257" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B259" r:id="rId258" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B260" r:id="rId259" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B261" r:id="rId260" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B262" r:id="rId261" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B263" r:id="rId262" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B264" r:id="rId263" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B265" r:id="rId264" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B266" r:id="rId265" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B267" r:id="rId266" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B268" r:id="rId267" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B269" r:id="rId268" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B270" r:id="rId269" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B271" r:id="rId270" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B272" r:id="rId271" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B273" r:id="rId272" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B274" r:id="rId273" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B275" r:id="rId274" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B276" r:id="rId275" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B277" r:id="rId276" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B278" r:id="rId277" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B279" r:id="rId278" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B280" r:id="rId279" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B281" r:id="rId280" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B282" r:id="rId281" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B283" r:id="rId282" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B284" r:id="rId283" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B285" r:id="rId284" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B286" r:id="rId285" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B287" r:id="rId286" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B288" r:id="rId287" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B289" r:id="rId288" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B290" r:id="rId289" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B291" r:id="rId290" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B292" r:id="rId291" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B293" r:id="rId292" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B294" r:id="rId293" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B295" r:id="rId294" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B296" r:id="rId295" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B297" r:id="rId296" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B298" r:id="rId297" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B299" r:id="rId298" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B300" r:id="rId299" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B301" r:id="rId300" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B302" r:id="rId301" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B303" r:id="rId302" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B304" r:id="rId303" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B305" r:id="rId304" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B306" r:id="rId305" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B307" r:id="rId306" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B308" r:id="rId307" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B309" r:id="rId308" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B310" r:id="rId309" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B311" r:id="rId310" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B312" r:id="rId311" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B313" r:id="rId312" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B314" r:id="rId313" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B315" r:id="rId314" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B316" r:id="rId315" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B317" r:id="rId316" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B318" r:id="rId317" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B319" r:id="rId318" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B320" r:id="rId319" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B321" r:id="rId320" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B322" r:id="rId321" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B323" r:id="rId322" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B324" r:id="rId323" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B325" r:id="rId324" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B326" r:id="rId325" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B327" r:id="rId326" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B328" r:id="rId327" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B329" r:id="rId328" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B330" r:id="rId329" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B331" r:id="rId330" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B332" r:id="rId331" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B333" r:id="rId332" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B334" r:id="rId333" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B335" r:id="rId334" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B336" r:id="rId335" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B337" r:id="rId336" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B338" r:id="rId337" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B339" r:id="rId338" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B340" r:id="rId339" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B341" r:id="rId340" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B342" r:id="rId341" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B343" r:id="rId342" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B344" r:id="rId343" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B345" r:id="rId344" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B346" r:id="rId345" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B347" r:id="rId346" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B348" r:id="rId347" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B349" r:id="rId348" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B350" r:id="rId349" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B351" r:id="rId350" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B352" r:id="rId351" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B353" r:id="rId352" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B354" r:id="rId353" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B355" r:id="rId354" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B356" r:id="rId355" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B357" r:id="rId356" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B358" r:id="rId357" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B359" r:id="rId358" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B360" r:id="rId359" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B361" r:id="rId360" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B362" r:id="rId361" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B363" r:id="rId362" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B364" r:id="rId363" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B365" r:id="rId364" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B366" r:id="rId365" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B367" r:id="rId366" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B368" r:id="rId367" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B369" r:id="rId368" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B370" r:id="rId369" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B371" r:id="rId370" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B372" r:id="rId371" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B373" r:id="rId372" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B374" r:id="rId373" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B375" r:id="rId374" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B376" r:id="rId375" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B377" r:id="rId376" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B378" r:id="rId377" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B379" r:id="rId378" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B380" r:id="rId379" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B381" r:id="rId380" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B382" r:id="rId381" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B383" r:id="rId382" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B384" r:id="rId383" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B385" r:id="rId384" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B386" r:id="rId385" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B387" r:id="rId386" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B388" r:id="rId387" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B389" r:id="rId388" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B390" r:id="rId389" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B391" r:id="rId390" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B392" r:id="rId391" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B393" r:id="rId392" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B394" r:id="rId393" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B395" r:id="rId394" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B396" r:id="rId395" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B397" r:id="rId396" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B398" r:id="rId397" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B399" r:id="rId398" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B400" r:id="rId399" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B401" r:id="rId400" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B402" r:id="rId401" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B403" r:id="rId402" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B404" r:id="rId403" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B405" r:id="rId404" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B406" r:id="rId405" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B407" r:id="rId406" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B408" r:id="rId407" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B409" r:id="rId408" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B410" r:id="rId409" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
+    <hyperlink ref="B411" r:id="rId410" location="IMGActivity-execute?IMGActivity=SIMG_CFMENUOLMSOMSF&amp;CustomizingObject=V023&amp;CustomizingObjectType=V&amp;CustomizingProject=&amp;CustomizingTransaction=S_ALR_87002257&amp;Type=SSCUI"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{ea60d57e-af5b-4752-ac57-3e4f28ca11dc}" enabled="1" method="Standard" siteId="{36da45f1-dd2c-4d1f-af13-5abe46b99921}" removed="0"/>
-</clbl:labelList>
 </file>